--- a/models/6752_DCF_Model_20260906.xlsx
+++ b/models/6752_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79E0EB7-05CF-4349-98B4-6AA2D78D98EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41F1829-2161-4141-8F6C-ADF7426ACB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
     <t>vs Current Price</t>
   </si>
   <si>
-    <t>DCF - Perpetuity Growth</t>
+    <t>DCF - Perpetuity Growth [参考・Target不算入 — 追補6 §X]</t>
   </si>
   <si>
     <t>DCF - Exit Multiple</t>
@@ -92,7 +92,7 @@
     <t>Comps - PER Median [参考・Target不算入]</t>
   </si>
   <si>
-    <t>Note: Target Mid は DCF 2法（PGM / Exit）の平均のみ。Comps 2法は [参考] で Target 不算入（EV&lt;ネットデットで株式価値が負になる手法は INVALID として平均から除外）</t>
+    <t>Note: Target Mid は DCF 2法（PGM / Exit）の平均のみ。Comps 2法は [参考] で Target 不算入（EV&lt;ネットデットで株式価値が負になる手法は INVALID として平均から除外） ■【追補6 §X】PGMとExitの乖離が **5.79倍** で 3.0倍を超えたため、**乖離そのものを裁定トリガーとする追補6 §X により中点平均を禁止**し、どちらの脚を落とすかを判定した。■**観測倍率バンドテスト**: Peer の実測 EV/EBITDA の第1〜第3四分位バンドは **(13.141973543373997, 15.552094158010673, 5)倍**。これに対し **PGM逆算 2.47倍 / 仮定Exit 14.30倍**。**PGM法のみがバンドの外にあるため PGM法を[参考]に降格し、Target = Exit 単独**とした。■バンドテストは市場倍率を無条件のアンカーにするものではない（それではスクリーナーが市場の複写に堕する）。**実際に取引されているレンジの外に出た脚だけを取り除く**という位置づけである。</t>
   </si>
   <si>
     <t>DCF Valuation Range (PGM - Exit)</t>
@@ -1666,7 +1666,7 @@
     <col min="3" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="45" t="s">
         <v>0</v>
       </c>
@@ -1674,19 +1674,19 @@
       <c r="D1" s="44"/>
       <c r="E1" s="44"/>
     </row>
-    <row r="3" spans="2:5" ht="18" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="43" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
     </row>
-    <row r="4" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
@@ -1718,16 +1718,16 @@
         <v>4163</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <f>IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0))</f>
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+        <f>IF(ISNUMBER(C17),ROUND(C17,0),"N/A")</f>
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>11</v>
       </c>
@@ -1736,23 +1736,23 @@
         <v>SELL</v>
       </c>
     </row>
-    <row r="12" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="7">
         <f>IF(ISNUMBER(C10),(C10-C9)/C9,"N/A")</f>
-        <v>-0.67403314917127077</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+        <v>-0.39923132356473695</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="10" t="s">
         <v>14</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>17</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>-0.94883497477780443</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>18</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>-0.39923132356473695</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>19</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>-0.1799183281287533</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>20</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>-0.48642805668988709</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="45" t="s">
         <v>21</v>
       </c>
@@ -1823,7 +1823,7 @@
       <c r="D20" s="44"/>
       <c r="E20" s="44"/>
     </row>
-    <row r="21" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>22</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>213 - 2501</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>23</v>
       </c>
@@ -1853,10 +1853,10 @@
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" t="str">
         <f>"At "&amp;TEXT(C9,"#,##0")&amp;" the market capitalises the depressed margin; a base case that returns to the four-year median supports "&amp;TEXT(C10,"#,##0")&amp;", or "&amp;TEXT(C12,"+0.0%;-0.0%")&amp;" from here."</f>
-        <v>At 4,163 the market capitalises the depressed margin; a base case that returns to the four-year median supports 1,357, or -67.4% from here.</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+        <v>At 4,163 the market capitalises the depressed margin; a base case that returns to the four-year median supports 2,501, or -39.9% from here.</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>25</v>
       </c>
@@ -1866,7 +1866,7 @@
     <row r="29" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B29" t="str">
         <f>"Capital expenditure reached ten percent of revenue on battery capacity and the base case assumes it halves over five years; if the ramp continues, the free cash flow behind "&amp;TEXT(C10,"#,##0")&amp;" does not appear."</f>
-        <v>Capital expenditure reached ten percent of revenue on battery capacity and the base case assumes it halves over five years; if the ramp continues, the free cash flow behind 1,357 does not appear.</v>
+        <v>Capital expenditure reached ten percent of revenue on battery capacity and the base case assumes it halves over five years; if the ramp continues, the free cash flow behind 2,501 does not appear.</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
@@ -1904,12 +1904,12 @@
     <col min="3" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="10" t="s">
         <v>28</v>
       </c>
@@ -1923,12 +1923,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>33</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>8048722</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>34</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>5521854</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>35</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>2526868</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>36</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>0.31394648740508119</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>37</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>2316905</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>38</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>209963</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>39</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>189540</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>40</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>2.608650168312435E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>41</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>2.3549080214225315E-2</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>42</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>-4.8410267687453039E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>44</v>
       </c>
@@ -2137,12 +2137,12 @@
         <v>-0.48352905292054293</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>46</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>624289</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>47</v>
       </c>
@@ -2168,7 +2168,7 @@
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
     </row>
-    <row r="21" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>48</v>
       </c>
@@ -2183,12 +2183,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>52</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>770179</v>
       </c>
     </row>
-    <row r="27" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>53</v>
       </c>
@@ -2214,12 +2214,12 @@
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
     </row>
-    <row r="28" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>55</v>
       </c>
@@ -2243,12 +2243,12 @@
     <col min="3" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
         <v>57</v>
       </c>
@@ -2258,7 +2258,7 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>58</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>59</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>60</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>2.9700000000000001E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>61</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>1.2636000000000001</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>62</v>
       </c>
@@ -2298,7 +2298,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>63</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>64</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>1.9900000000000001E-2</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>65</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>8.5699999999999998E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>66</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>67</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>68</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>2334925020</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>69</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>833018</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>70</v>
       </c>
@@ -2362,7 +2362,7 @@
         <v>8048722</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>71</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>72</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>73</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>8048722</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>74</v>
       </c>
@@ -2396,7 +2396,7 @@
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>75</v>
       </c>
@@ -2405,7 +2405,7 @@
         <v>0.12183400000000001</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>76</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>0.9210647508519848</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>77</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>7.8935249148015099E-2</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>78</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>0.11378781431334622</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>79</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>81</v>
       </c>
@@ -2454,7 +2454,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="10" t="s">
         <v>82</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>42</v>
       </c>
@@ -2496,7 +2496,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="31" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
         <v>87</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>0.68600000000000005</v>
       </c>
     </row>
-    <row r="32" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>88</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>0.27689999999999998</v>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
         <v>33</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>8885796.754407702</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>34</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>6095656.5735236844</v>
       </c>
     </row>
-    <row r="35" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>35</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>2790140.1808840176</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>36</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>0.31399999999999989</v>
       </c>
     </row>
-    <row r="37" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
         <v>89</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>2460477.1212954926</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>90</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>3.7099999999999911E-2</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>91</v>
       </c>
@@ -2721,7 +2721,7 @@
         <v>329663.05958852498</v>
       </c>
     </row>
-    <row r="40" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>92</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>82415.764897131245</v>
       </c>
     </row>
-    <row r="41" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>93</v>
       </c>
@@ -2771,7 +2771,7 @@
         <v>247247.29469139373</v>
       </c>
     </row>
-    <row r="42" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>94</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>444289.83772038511</v>
       </c>
     </row>
-    <row r="43" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>95</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>466000</v>
       </c>
     </row>
-    <row r="44" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
         <v>96</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>29145.795231298544</v>
       </c>
     </row>
-    <row r="45" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
         <v>97</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>196391.33718048036</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
         <v>98</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>0.58342856640709695</v>
       </c>
     </row>
-    <row r="47" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
         <v>99</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>114580.31630598045</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="22" t="s">
         <v>100</v>
       </c>
@@ -2926,7 +2926,7 @@
       <c r="F49" s="23"/>
       <c r="G49" s="23"/>
     </row>
-    <row r="50" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
         <v>101</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>215644.05850265716</v>
       </c>
     </row>
-    <row r="51" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>102</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>1911161.2655550293</v>
       </c>
     </row>
-    <row r="52" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
         <v>103</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>1115026.0773355439</v>
       </c>
     </row>
-    <row r="53" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
         <v>104</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>1330670.135838201</v>
       </c>
     </row>
-    <row r="54" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
         <v>105</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>497652.13583820104</v>
       </c>
     </row>
-    <row r="55" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
         <v>106</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="57" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="22" t="s">
         <v>107</v>
       </c>
@@ -2990,7 +2990,7 @@
       <c r="F57" s="23"/>
       <c r="G57" s="23"/>
     </row>
-    <row r="58" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
         <v>101</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>215644.05850265716</v>
       </c>
     </row>
-    <row r="59" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
         <v>108</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>773952.89730891003</v>
       </c>
     </row>
-    <row r="60" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
         <v>109</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>11067526.431517415</v>
       </c>
     </row>
-    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
         <v>103</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>6457111.0796128586</v>
       </c>
     </row>
-    <row r="62" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
         <v>104</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>6672755.1381155159</v>
       </c>
     </row>
-    <row r="63" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
         <v>105</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>5839737.1381155159</v>
       </c>
     </row>
-    <row r="64" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="4" t="s">
         <v>110</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>2501</v>
       </c>
     </row>
-    <row r="66" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="22" t="s">
         <v>111</v>
       </c>
@@ -3063,7 +3063,7 @@
       <c r="F66" s="23"/>
       <c r="G66" s="23"/>
     </row>
-    <row r="67" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="25" t="s">
         <v>112</v>
       </c>
@@ -3080,12 +3080,12 @@
         <v>116</v>
       </c>
     </row>
-    <row r="68" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="69" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="4" t="s">
         <v>80</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="70" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="4" t="s">
         <v>117</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="71" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="4" t="s">
         <v>118</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="72" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
         <v>119</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="73" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
         <v>120</v>
       </c>
@@ -3185,12 +3185,12 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="75" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="76" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="4" t="s">
         <v>80</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>0.68600000000000005</v>
       </c>
     </row>
-    <row r="77" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="4" t="s">
         <v>117</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="78" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="s">
         <v>118</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>0.68600000000000005</v>
       </c>
     </row>
-    <row r="79" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="4" t="s">
         <v>119</v>
       </c>
@@ -3270,7 +3270,7 @@
         <v>0.69399999999999995</v>
       </c>
     </row>
-    <row r="80" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="4" t="s">
         <v>120</v>
       </c>
@@ -3290,12 +3290,12 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="82" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="83" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="4" t="s">
         <v>80</v>
       </c>
@@ -3315,7 +3315,7 @@
         <v>0.27689999999999998</v>
       </c>
     </row>
-    <row r="84" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="4" t="s">
         <v>117</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>0.27189999999999998</v>
       </c>
     </row>
-    <row r="85" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="4" t="s">
         <v>118</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>0.27689999999999998</v>
       </c>
     </row>
-    <row r="86" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="4" t="s">
         <v>119</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>0.28699999999999998</v>
       </c>
     </row>
-    <row r="87" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="4" t="s">
         <v>120</v>
       </c>
@@ -3419,17 +3419,17 @@
     <col min="3" max="9" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="8" t="s">
         <v>123</v>
       </c>
@@ -3441,7 +3441,7 @@
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>124</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>4163</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>68</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>2334925020</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>125</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>9720292.8582600001</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>69</v>
       </c>
@@ -3477,7 +3477,7 @@
         <v>833018</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>126</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>10553310.85826</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>127</v>
       </c>
@@ -3495,7 +3495,7 @@
         <v>0.11378781431334622</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>128</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>129</v>
       </c>
@@ -3513,7 +3513,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>130</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>209963</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>131</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>406534</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>132</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>8885796.754407702</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>133</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>1330670.135838201</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>134</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>4.8063975900267022E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>135</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>9222640.7224217989</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>136</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>3950</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>137</v>
       </c>
@@ -3585,12 +3585,12 @@
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>139</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>1095305.0677481093</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>140</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>1460406.7569974791</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
         <v>141</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>3.5923360825846773</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
         <v>142</v>
       </c>
@@ -3626,7 +3626,7 @@
         <v>6.9555433909664046</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
         <v>143</v>
       </c>
@@ -3635,7 +3635,7 @@
         <v>0.16435293281641405</v>
       </c>
     </row>
-    <row r="29" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
         <v>144</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>30384643.168676477</v>
       </c>
     </row>
-    <row r="32" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
         <v>145</v>
       </c>
@@ -3656,17 +3656,17 @@
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="28" t="s">
         <v>148</v>
       </c>
@@ -3694,12 +3694,12 @@
         <v>0.13378781431334621</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>151</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>0.84730705691587027</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>152</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>1.5678366259977412</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>153</v>
       </c>
@@ -3783,7 +3783,7 @@
         <v>2.1828410233413087</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>154</v>
       </c>
@@ -3811,12 +3811,12 @@
         <v>2.9448211530704009</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>151</v>
       </c>
@@ -3844,7 +3844,7 @@
         <v>7.0969383943093378</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
         <v>152</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>6.2720939612975473</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
         <v>153</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>5.5759406660603563</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
         <v>154</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>4.724739246130703</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="22" t="s">
         <v>156</v>
       </c>
@@ -3940,7 +3940,7 @@
       <c r="H47" s="23"/>
       <c r="I47" s="23"/>
     </row>
-    <row r="48" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
         <v>151</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>1957629.7891913012</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
         <v>152</v>
       </c>
@@ -3996,7 +3996,7 @@
         <v>2190957.8440051675</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
         <v>153</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>2441339.6967118131</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>154</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>2847305.8426666865</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="22" t="s">
         <v>157</v>
       </c>
@@ -4064,7 +4064,7 @@
       <c r="H52" s="23"/>
       <c r="I52" s="23"/>
     </row>
-    <row r="53" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
         <v>151</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>4.8154146742739874</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
         <v>152</v>
       </c>
@@ -4120,7 +4120,7 @@
         <v>5.3893594238247413</v>
       </c>
     </row>
-    <row r="55" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
         <v>153</v>
       </c>
@@ -4148,7 +4148,7 @@
         <v>6.0052534270486921</v>
       </c>
     </row>
-    <row r="56" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
         <v>154</v>
       </c>
@@ -4176,7 +4176,7 @@
         <v>7.0038566089593655</v>
       </c>
     </row>
-    <row r="58" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
         <v>158</v>
       </c>
@@ -4188,12 +4188,12 @@
       <c r="H58" s="9"/>
       <c r="I58" s="9"/>
     </row>
-    <row r="59" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="60" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
         <v>160</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>1779244.999805788</v>
       </c>
     </row>
-    <row r="62" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="28" t="s">
         <v>161</v>
       </c>
@@ -4213,7 +4213,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="63" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="31">
         <v>2.4E-2</v>
       </c>
@@ -4226,7 +4226,7 @@
         <v>9.2108049358943145</v>
       </c>
     </row>
-    <row r="64" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="31">
         <v>3.5999999999999997E-2</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>6.1405366239295445</v>
       </c>
     </row>
-    <row r="65" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="4" t="s">
         <v>164</v>
       </c>
@@ -4252,7 +4252,7 @@
         <v>4.5992724139210361</v>
       </c>
     </row>
-    <row r="66" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="31">
         <v>6.0100000000000001E-2</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>3.6781916549328382</v>
       </c>
     </row>
-    <row r="67" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="31">
         <v>7.2099999999999997E-2</v>
       </c>
@@ -4278,7 +4278,7 @@
         <v>3.0660099647914505</v>
       </c>
     </row>
-    <row r="69" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="8" t="s">
         <v>165</v>
       </c>
@@ -4290,7 +4290,7 @@
       <c r="H69" s="9"/>
       <c r="I69" s="9"/>
     </row>
-    <row r="70" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="6" t="s">
         <v>166</v>
       </c>
@@ -4299,7 +4299,7 @@
         <v>17.179269024767827</v>
       </c>
     </row>
-    <row r="71" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="6" t="s">
         <v>167</v>
       </c>
@@ -4308,7 +4308,7 @@
         <v>1.3111784527108776</v>
       </c>
     </row>
-    <row r="72" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
         <v>168</v>
       </c>
@@ -4317,7 +4317,7 @@
         <v>5.5406781781028087</v>
       </c>
     </row>
-    <row r="73" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
         <v>169</v>
       </c>
@@ -4326,7 +4326,7 @@
         <v>4.7461864235962423</v>
       </c>
     </row>
-    <row r="74" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="4" t="s">
         <v>170</v>
       </c>
@@ -4335,12 +4335,12 @@
         <v>14.333259113904496</v>
       </c>
     </row>
-    <row r="75" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="77" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="22" t="s">
         <v>172</v>
       </c>
@@ -4352,13 +4352,13 @@
       <c r="H77" s="23"/>
       <c r="I77" s="23"/>
     </row>
-    <row r="78" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="str">
         <f>"At "&amp;TEXT(C6,"#,##0")&amp;" yen the market is paying for a steady-state operating profit of "&amp;TEXT(F49,"#,##0")&amp;" mn JPY - "&amp;TEXT(F54,"0.00")&amp;"x the FY2025 cycle peak of "&amp;TEXT(C15,"#,##0")&amp;" mn - reached in 5 years and sustained for ever, against "&amp;TEXT(C14,"#,##0")&amp;" mn actually earned in FY2026."</f>
         <v>At 4,163 yen the market is paying for a steady-state operating profit of 1,779,245 mn JPY - 4.38x the FY2025 cycle peak of 406,534 mn - reached in 5 years and sustained for ever, against 209,963 mn actually earned in FY2026.</v>
       </c>
     </row>
-    <row r="79" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="4" t="str">
         <f>"Even with no ramp at all (Block A) the price needs "&amp;TEXT(C25,"#,##0")&amp;" mn, or "&amp;TEXT(C26,"0.00")&amp;"x the peak. The base case supports an EV of only "&amp;TEXT(C17,"#,##0")&amp;" mn, leaving "&amp;TEXT(C20,"#,##0")&amp;" yen per share of the current price unexplained by mid-cycle economics."</f>
         <v>Even with no ramp at all (Block A) the price needs 1,460,407 mn, or 3.59x the peak. The base case supports an EV of only 1,330,670 mn, leaving 3,950 yen per share of the current price unexplained by mid-cycle economics.</v>
@@ -4383,12 +4383,12 @@
     <col min="3" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
         <v>174</v>
       </c>
@@ -4411,7 +4411,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="33" t="s">
         <v>176</v>
       </c>
@@ -4440,7 +4440,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="33" t="s">
         <v>177</v>
       </c>
@@ -4469,7 +4469,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="33" t="s">
         <v>178</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
         <v>179</v>
       </c>
@@ -4509,7 +4509,7 @@
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
     </row>
-    <row r="9" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="33" t="s">
         <v>33</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>8885796.754407702</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="33" t="s">
         <v>34</v>
       </c>
@@ -4565,7 +4565,7 @@
         <v>6095656.5735236844</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>180</v>
       </c>
@@ -4576,7 +4576,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="33" t="s">
         <v>181</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>1436334.2698905601</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="33" t="s">
         <v>182</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>1185730.4567676208</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="33" t="s">
         <v>183</v>
       </c>
@@ -4661,7 +4661,7 @@
         <v>2622064.7266581808</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="33" t="s">
         <v>184</v>
       </c>
@@ -4689,7 +4689,7 @@
         <v>1135629.1698619467</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="33" t="s">
         <v>185</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>1135629.1698619467</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="22" t="s">
         <v>186</v>
       </c>
@@ -4729,7 +4729,7 @@
       <c r="G17" s="23"/>
       <c r="H17" s="23"/>
     </row>
-    <row r="18" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="33" t="s">
         <v>187</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>1486435.5567962341</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="33" t="s">
         <v>96</v>
       </c>
@@ -4786,7 +4786,7 @@
         <v>29145.795231298544</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="22" t="s">
         <v>188</v>
       </c>
@@ -4797,7 +4797,7 @@
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
     </row>
-    <row r="23" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D23" s="25" t="s">
         <v>82</v>
       </c>
@@ -4814,12 +4814,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>80</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>117</v>
       </c>
@@ -4859,7 +4859,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>118</v>
       </c>
@@ -4879,7 +4879,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>119</v>
       </c>
@@ -4899,7 +4899,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
         <v>120</v>
       </c>
@@ -4919,12 +4919,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>80</v>
       </c>
@@ -4944,7 +4944,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
         <v>117</v>
       </c>
@@ -4964,7 +4964,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>118</v>
       </c>
@@ -4984,7 +4984,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>119</v>
       </c>
@@ -5004,7 +5004,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>120</v>
       </c>
@@ -5024,12 +5024,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="39" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>80</v>
       </c>
@@ -5049,7 +5049,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>117</v>
       </c>
@@ -5069,7 +5069,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>118</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>119</v>
       </c>
@@ -5109,7 +5109,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="43" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>120</v>
       </c>
@@ -5150,17 +5150,17 @@
     <col min="17" max="17" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="28" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" ht="28" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
         <v>3</v>
       </c>
@@ -5210,7 +5210,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>208</v>
       </c>
@@ -5265,7 +5265,7 @@
         <v>5211272</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>210</v>
       </c>
@@ -5318,7 +5318,7 @@
         <v>6568369</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>212</v>
       </c>
@@ -5371,7 +5371,7 @@
         <v>4484266</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>214</v>
       </c>
@@ -5424,7 +5424,7 @@
         <v>2024915</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>216</v>
       </c>
@@ -5477,7 +5477,7 @@
         <v>2196578</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>218</v>
       </c>
@@ -5530,12 +5530,12 @@
         <v>2718743</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="15" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>221</v>
       </c>
@@ -5564,7 +5564,7 @@
         <v>9.0930823461409294E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>222</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>0.12215635266532682</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>223</v>
       </c>
@@ -5622,7 +5622,7 @@
         <v>0.12302226463162245</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="22" t="s">
         <v>224</v>
       </c>
@@ -5634,12 +5634,12 @@
       <c r="H19" s="23"/>
       <c r="I19" s="23"/>
     </row>
-    <row r="20" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>226</v>
       </c>
@@ -5647,7 +5647,7 @@
         <v>614305</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
         <v>227</v>
       </c>
@@ -5655,7 +5655,7 @@
         <v>189540</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>228</v>
       </c>
@@ -5663,7 +5663,7 @@
         <v>2334925020</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>69</v>
       </c>
@@ -5671,12 +5671,12 @@
         <v>833018</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>230</v>
       </c>
@@ -5685,7 +5685,7 @@
         <v>3414</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>231</v>
       </c>
@@ -5713,12 +5713,12 @@
     <col min="3" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>233</v>
       </c>
@@ -5741,12 +5741,12 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="40" t="s">
         <v>237</v>
       </c>
@@ -5779,7 +5779,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="39">
         <f>$C$3-0.015</f>
         <v>9.8787814313346226E-2</v>
@@ -5813,7 +5813,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="39">
         <f>$C$3-0.01</f>
         <v>0.10378781431334623</v>
@@ -5847,7 +5847,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="39">
         <f>$C$3-0.005</f>
         <v>0.10878781431334622</v>
@@ -5881,7 +5881,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="39">
         <f>$C$3</f>
         <v>0.11378781431334622</v>
@@ -5915,7 +5915,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="39">
         <f>$C$3+0.005</f>
         <v>0.11878781431334623</v>
@@ -5949,7 +5949,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="39">
         <f>$C$3+0.01</f>
         <v>0.12378781431334622</v>
@@ -5983,7 +5983,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="39">
         <f>$C$3+0.015</f>
         <v>0.12878781431334624</v>
@@ -6017,12 +6017,12 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="40" t="s">
         <v>239</v>
       </c>
@@ -6055,7 +6055,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="39">
         <f>$C$3-0.015</f>
         <v>9.8787814313346226E-2</v>
@@ -6089,7 +6089,7 @@
         <v>3322</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="39">
         <f>$C$3-0.01</f>
         <v>0.10378781431334623</v>
@@ -6123,7 +6123,7 @@
         <v>3240</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="39">
         <f>$C$3-0.005</f>
         <v>0.10878781431334622</v>
@@ -6157,7 +6157,7 @@
         <v>3159</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="39">
         <f>$C$3</f>
         <v>0.11378781431334622</v>
@@ -6191,7 +6191,7 @@
         <v>3081</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="39">
         <f>$C$3+0.005</f>
         <v>0.11878781431334623</v>
@@ -6225,7 +6225,7 @@
         <v>3005</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="39">
         <f>$C$3+0.01</f>
         <v>0.12378781431334622</v>
@@ -6259,7 +6259,7 @@
         <v>2931</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="39">
         <f>$C$3+0.015</f>
         <v>0.12878781431334624</v>
@@ -6293,7 +6293,7 @@
         <v>2859</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="45" t="s">
         <v>240</v>
       </c>
@@ -6330,12 +6330,12 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
         <v>242</v>
       </c>
@@ -6415,12 +6415,12 @@
         <v>262</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="8" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="10" t="s">
         <v>264</v>
       </c>
@@ -6428,7 +6428,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>266</v>
       </c>
@@ -6436,7 +6436,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>268</v>
       </c>
@@ -6444,7 +6444,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>270</v>
       </c>
@@ -6452,7 +6452,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>272</v>
       </c>
@@ -6460,7 +6460,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>273</v>
       </c>
@@ -6468,7 +6468,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>275</v>
       </c>
@@ -6476,7 +6476,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>277</v>
       </c>
@@ -6484,7 +6484,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>279</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
         <v>281</v>
       </c>
@@ -6500,7 +6500,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>282</v>
       </c>
@@ -6508,7 +6508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>283</v>
       </c>
@@ -6516,7 +6516,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="25" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>284</v>
       </c>
@@ -6524,7 +6524,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="26" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>286</v>
       </c>
@@ -6532,7 +6532,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="27" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>287</v>
       </c>
@@ -6540,7 +6540,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="28" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>288</v>
       </c>
@@ -6548,7 +6548,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="29" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
         <v>290</v>
       </c>
@@ -6556,7 +6556,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="30" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>292</v>
       </c>
@@ -6564,7 +6564,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="31" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
         <v>294</v>
       </c>
@@ -6572,7 +6572,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="32" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>295</v>
       </c>
@@ -6580,7 +6580,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="33" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
         <v>296</v>
       </c>
@@ -6588,7 +6588,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="34" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>297</v>
       </c>
@@ -6596,7 +6596,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="35" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>299</v>
       </c>
@@ -6604,7 +6604,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="36" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>301</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="37" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
         <v>303</v>
       </c>
@@ -6620,7 +6620,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="38" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>305</v>
       </c>
@@ -6628,7 +6628,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="39" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>307</v>
       </c>
@@ -6636,7 +6636,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="40" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>309</v>
       </c>
@@ -6644,7 +6644,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="41" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>311</v>
       </c>
@@ -6652,7 +6652,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="42" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>313</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="43" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>315</v>
       </c>
@@ -6668,7 +6668,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="44" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
         <v>317</v>
       </c>
@@ -6676,7 +6676,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="45" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
         <v>318</v>
       </c>
@@ -6684,7 +6684,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="46" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
         <v>320</v>
       </c>
@@ -6692,7 +6692,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="47" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
         <v>322</v>
       </c>
@@ -6700,7 +6700,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="48" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
         <v>324</v>
       </c>
@@ -6708,7 +6708,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="49" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
         <v>326</v>
       </c>
@@ -6716,7 +6716,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="50" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
         <v>328</v>
       </c>
@@ -6724,7 +6724,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="51" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>330</v>
       </c>
@@ -6732,7 +6732,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="52" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
         <v>332</v>
       </c>
@@ -6740,7 +6740,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="53" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
         <v>334</v>
       </c>
@@ -6748,7 +6748,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="54" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
         <v>336</v>
       </c>
@@ -6756,7 +6756,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="55" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
         <v>338</v>
       </c>
@@ -6764,7 +6764,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="56" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
         <v>340</v>
       </c>
@@ -6772,7 +6772,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="57" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="4" t="s">
         <v>342</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="58" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
         <v>344</v>
       </c>
@@ -6788,7 +6788,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="59" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
         <v>346</v>
       </c>
@@ -6796,7 +6796,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="60" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
         <v>348</v>
       </c>
@@ -6804,7 +6804,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="61" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
         <v>350</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="62" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
         <v>352</v>
       </c>
@@ -6820,7 +6820,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="63" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
         <v>354</v>
       </c>
@@ -6828,7 +6828,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="64" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="4" t="s">
         <v>356</v>
       </c>
